--- a/electrician_forms/010_extension_cord_safety_checklist--electrician_forms.xlsx
+++ b/electrician_forms/010_extension_cord_safety_checklist--electrician_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'safety_officer',_'value':_1}</t>
+          <t>safety_officer</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Safety Officer', 'value': 1}</t>
+          <t>Safety Officer</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'safety_inspector',_'value':_2}</t>
+          <t>safety_inspector</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Safety Inspector', 'value': 2}</t>
+          <t>Safety Inspector</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'facility_team',_'value':_3}</t>
+          <t>facility_team</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Facility Team', 'value': 3}</t>
+          <t>Facility Team</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'none',_'value':_0}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'None', 'value': 0}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good',_'value':_1}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good', 'value': 1}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'hazardous',_'value':_2}</t>
+          <t>hazardous</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Hazardous', 'value': 2}</t>
+          <t>Hazardous</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_inspected',_'value':_3}</t>
+          <t>not_inspected</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not Inspected', 'value': 3}</t>
+          <t>Not Inspected</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'power',_'value':_1}</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Power', 'value': 1}</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'non-power',_'value':_2}</t>
+          <t>non-power</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Non-Power', 'value': 2}</t>
+          <t>Non-Power</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good',_'value':_1}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good', 'value': 1}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'damaged',_'value':_2}</t>
+          <t>damaged</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Damaged', 'value': 2}</t>
+          <t>Damaged</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_inspected',_'value':_3}</t>
+          <t>not_inspected</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not Inspected', 'value': 3}</t>
+          <t>Not Inspected</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'water',_'value':_1}</t>
+          <t>water</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Water', 'value': 1}</t>
+          <t>Water</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fire',_'value':_2}</t>
+          <t>fire</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fire', 'value': 2}</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'electrical',_'value':_3}</t>
+          <t>electrical</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Electrical', 'value': 3}</t>
+          <t>Electrical</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other',_'value':_4}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other', 'value': 4}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
